--- a/경기철도-용인시-보고서.xlsx
+++ b/경기철도-용인시-보고서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 내 문서 모음\01. 업무관련 문서양식\017 지하안전점검(지하안전법) 관련\■ 연도별 지하안전점검(육안점검) 결과보고서\2026년 지하안전점검 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE338F5-918A-4936-BE16-247D1CB92420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C01BC4-C36E-454E-9680-D3DB49F23AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="595">
   <si>
     <t>시행년도</t>
   </si>
@@ -856,9 +856,6 @@
   </si>
   <si>
     <t>26-용인시-08</t>
-  </si>
-  <si>
-    <t>긴급</t>
   </si>
   <si>
     <t>상선종점 피난계단 뒤 보도</t>
@@ -2309,16 +2306,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2698,7 +2695,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -2777,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D5" t="s">
         <v>248</v>
@@ -3046,7 +3043,7 @@
         <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G9" t="s">
         <v>34</v>
@@ -3079,10 +3076,10 @@
         <v>29</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="S9" t="s">
         <v>32</v>
@@ -3238,10 +3235,10 @@
         <v>270</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G12" t="s">
         <v>34</v>
@@ -3271,10 +3268,10 @@
         <v>4</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R12" t="s">
         <v>268</v>
@@ -3283,7 +3280,7 @@
         <v>32</v>
       </c>
       <c r="T12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U12" t="s">
         <v>259</v>
@@ -3300,7 +3297,7 @@
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -3342,13 +3339,13 @@
         <v>27</v>
       </c>
       <c r="R13" t="s">
+        <v>273</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" t="s">
         <v>274</v>
-      </c>
-      <c r="S13" t="s">
-        <v>32</v>
-      </c>
-      <c r="T13" t="s">
-        <v>275</v>
       </c>
       <c r="U13" t="s">
         <v>32</v>
@@ -3365,7 +3362,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E14" t="s">
         <v>34</v>
@@ -3407,13 +3404,13 @@
         <v>27</v>
       </c>
       <c r="R14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S14" t="s">
         <v>32</v>
       </c>
       <c r="T14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U14" t="s">
         <v>32</v>
@@ -3430,7 +3427,7 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E15" t="s">
         <v>34</v>
@@ -3472,13 +3469,13 @@
         <v>27</v>
       </c>
       <c r="R15" t="s">
+        <v>278</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" t="s">
         <v>279</v>
-      </c>
-      <c r="S15" t="s">
-        <v>32</v>
-      </c>
-      <c r="T15" t="s">
-        <v>280</v>
       </c>
       <c r="U15" t="s">
         <v>32</v>
@@ -3495,13 +3492,13 @@
         <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G16" t="s">
         <v>34</v>
@@ -3537,13 +3534,13 @@
         <v>263</v>
       </c>
       <c r="R16" t="s">
+        <v>281</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" t="s">
         <v>282</v>
-      </c>
-      <c r="S16" t="s">
-        <v>32</v>
-      </c>
-      <c r="T16" t="s">
-        <v>283</v>
       </c>
       <c r="U16" t="s">
         <v>32</v>
@@ -3560,7 +3557,7 @@
         <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E17" t="s">
         <v>34</v>
@@ -3602,13 +3599,13 @@
         <v>27</v>
       </c>
       <c r="R17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S17" t="s">
         <v>32</v>
       </c>
       <c r="T17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U17" t="s">
         <v>32</v>
@@ -3625,13 +3622,13 @@
         <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G18" t="s">
         <v>34</v>
@@ -3667,13 +3664,13 @@
         <v>263</v>
       </c>
       <c r="R18" t="s">
+        <v>286</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" t="s">
         <v>287</v>
-      </c>
-      <c r="S18" t="s">
-        <v>32</v>
-      </c>
-      <c r="T18" t="s">
-        <v>288</v>
       </c>
       <c r="U18" t="s">
         <v>32</v>
@@ -3690,7 +3687,7 @@
         <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E19" t="s">
         <v>34</v>
@@ -3732,13 +3729,13 @@
         <v>27</v>
       </c>
       <c r="R19" t="s">
+        <v>289</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" t="s">
         <v>290</v>
-      </c>
-      <c r="S19" t="s">
-        <v>32</v>
-      </c>
-      <c r="T19" t="s">
-        <v>291</v>
       </c>
       <c r="U19" t="s">
         <v>32</v>
@@ -3755,7 +3752,7 @@
         <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E20" t="s">
         <v>34</v>
@@ -3797,13 +3794,13 @@
         <v>27</v>
       </c>
       <c r="R20" t="s">
+        <v>292</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
         <v>293</v>
-      </c>
-      <c r="S20" t="s">
-        <v>32</v>
-      </c>
-      <c r="T20" t="s">
-        <v>294</v>
       </c>
       <c r="U20" t="s">
         <v>32</v>
@@ -3820,7 +3817,7 @@
         <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E21" t="s">
         <v>34</v>
@@ -3862,13 +3859,13 @@
         <v>27</v>
       </c>
       <c r="R21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" t="s">
         <v>296</v>
-      </c>
-      <c r="S21" t="s">
-        <v>32</v>
-      </c>
-      <c r="T21" t="s">
-        <v>297</v>
       </c>
       <c r="U21" t="s">
         <v>32</v>
@@ -3885,7 +3882,7 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E22" t="s">
         <v>34</v>
@@ -3927,13 +3924,13 @@
         <v>27</v>
       </c>
       <c r="R22" t="s">
+        <v>298</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
         <v>299</v>
-      </c>
-      <c r="S22" t="s">
-        <v>32</v>
-      </c>
-      <c r="T22" t="s">
-        <v>300</v>
       </c>
       <c r="U22" t="s">
         <v>32</v>
@@ -3950,7 +3947,7 @@
         <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E23" t="s">
         <v>34</v>
@@ -3992,13 +3989,13 @@
         <v>27</v>
       </c>
       <c r="R23" t="s">
+        <v>301</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" t="s">
         <v>302</v>
-      </c>
-      <c r="S23" t="s">
-        <v>32</v>
-      </c>
-      <c r="T23" t="s">
-        <v>303</v>
       </c>
       <c r="U23" t="s">
         <v>32</v>
@@ -4015,7 +4012,7 @@
         <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
@@ -4057,13 +4054,13 @@
         <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S24" t="s">
         <v>32</v>
       </c>
       <c r="T24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="U24" t="s">
         <v>32</v>
@@ -4080,7 +4077,7 @@
         <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
@@ -4122,13 +4119,13 @@
         <v>263</v>
       </c>
       <c r="R25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S25" t="s">
         <v>32</v>
       </c>
       <c r="T25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="U25" t="s">
         <v>32</v>
@@ -4145,7 +4142,7 @@
         <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E26" t="s">
         <v>34</v>
@@ -4187,13 +4184,13 @@
         <v>27</v>
       </c>
       <c r="R26" t="s">
+        <v>308</v>
+      </c>
+      <c r="S26" t="s">
+        <v>32</v>
+      </c>
+      <c r="T26" t="s">
         <v>309</v>
-      </c>
-      <c r="S26" t="s">
-        <v>32</v>
-      </c>
-      <c r="T26" t="s">
-        <v>310</v>
       </c>
       <c r="U26" t="s">
         <v>32</v>
@@ -4210,7 +4207,7 @@
         <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E27" t="s">
         <v>34</v>
@@ -4252,13 +4249,13 @@
         <v>27</v>
       </c>
       <c r="R27" t="s">
+        <v>311</v>
+      </c>
+      <c r="S27" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" t="s">
         <v>312</v>
-      </c>
-      <c r="S27" t="s">
-        <v>32</v>
-      </c>
-      <c r="T27" t="s">
-        <v>313</v>
       </c>
       <c r="U27" t="s">
         <v>32</v>
@@ -4275,13 +4272,13 @@
         <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E28" t="s">
         <v>34</v>
       </c>
       <c r="F28" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G28" t="s">
         <v>34</v>
@@ -4317,13 +4314,13 @@
         <v>263</v>
       </c>
       <c r="R28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S28" t="s">
         <v>32</v>
       </c>
       <c r="T28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U28" t="s">
         <v>32</v>
@@ -4340,7 +4337,7 @@
         <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E29" t="s">
         <v>34</v>
@@ -4382,13 +4379,13 @@
         <v>27</v>
       </c>
       <c r="R29" t="s">
+        <v>316</v>
+      </c>
+      <c r="S29" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" t="s">
         <v>317</v>
-      </c>
-      <c r="S29" t="s">
-        <v>32</v>
-      </c>
-      <c r="T29" t="s">
-        <v>318</v>
       </c>
       <c r="U29" t="s">
         <v>32</v>
@@ -4405,7 +4402,7 @@
         <v>59</v>
       </c>
       <c r="D30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E30" t="s">
         <v>34</v>
@@ -4447,13 +4444,13 @@
         <v>27</v>
       </c>
       <c r="R30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S30" t="s">
         <v>32</v>
       </c>
       <c r="T30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U30" t="s">
         <v>32</v>
@@ -4470,7 +4467,7 @@
         <v>59</v>
       </c>
       <c r="D31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E31" t="s">
         <v>34</v>
@@ -4512,13 +4509,13 @@
         <v>27</v>
       </c>
       <c r="R31" t="s">
+        <v>321</v>
+      </c>
+      <c r="S31" t="s">
+        <v>32</v>
+      </c>
+      <c r="T31" t="s">
         <v>322</v>
-      </c>
-      <c r="S31" t="s">
-        <v>32</v>
-      </c>
-      <c r="T31" t="s">
-        <v>323</v>
       </c>
       <c r="U31" t="s">
         <v>32</v>
@@ -4535,7 +4532,7 @@
         <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E32" t="s">
         <v>34</v>
@@ -4577,13 +4574,13 @@
         <v>263</v>
       </c>
       <c r="R32" t="s">
+        <v>324</v>
+      </c>
+      <c r="S32" t="s">
+        <v>32</v>
+      </c>
+      <c r="T32" t="s">
         <v>325</v>
-      </c>
-      <c r="S32" t="s">
-        <v>32</v>
-      </c>
-      <c r="T32" t="s">
-        <v>326</v>
       </c>
       <c r="U32" t="s">
         <v>32</v>
@@ -4600,7 +4597,7 @@
         <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E33" t="s">
         <v>34</v>
@@ -4665,7 +4662,7 @@
         <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E34" t="s">
         <v>34</v>
@@ -4707,13 +4704,13 @@
         <v>27</v>
       </c>
       <c r="R34" t="s">
+        <v>328</v>
+      </c>
+      <c r="S34" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" t="s">
         <v>329</v>
-      </c>
-      <c r="S34" t="s">
-        <v>32</v>
-      </c>
-      <c r="T34" t="s">
-        <v>330</v>
       </c>
       <c r="U34" t="s">
         <v>32</v>
@@ -4730,7 +4727,7 @@
         <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E35" t="s">
         <v>34</v>
@@ -4772,13 +4769,13 @@
         <v>27</v>
       </c>
       <c r="R35" t="s">
+        <v>331</v>
+      </c>
+      <c r="S35" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" t="s">
         <v>332</v>
-      </c>
-      <c r="S35" t="s">
-        <v>32</v>
-      </c>
-      <c r="T35" t="s">
-        <v>333</v>
       </c>
       <c r="U35" t="s">
         <v>32</v>
@@ -4795,7 +4792,7 @@
         <v>59</v>
       </c>
       <c r="D36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E36" t="s">
         <v>34</v>
@@ -4837,13 +4834,13 @@
         <v>27</v>
       </c>
       <c r="R36" t="s">
+        <v>334</v>
+      </c>
+      <c r="S36" t="s">
+        <v>32</v>
+      </c>
+      <c r="T36" t="s">
         <v>335</v>
-      </c>
-      <c r="S36" t="s">
-        <v>32</v>
-      </c>
-      <c r="T36" t="s">
-        <v>336</v>
       </c>
       <c r="U36" t="s">
         <v>32</v>
@@ -4860,7 +4857,7 @@
         <v>59</v>
       </c>
       <c r="D37" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E37" t="s">
         <v>34</v>
@@ -4902,13 +4899,13 @@
         <v>27</v>
       </c>
       <c r="R37" t="s">
+        <v>337</v>
+      </c>
+      <c r="S37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" t="s">
         <v>338</v>
-      </c>
-      <c r="S37" t="s">
-        <v>32</v>
-      </c>
-      <c r="T37" t="s">
-        <v>339</v>
       </c>
       <c r="U37" t="s">
         <v>32</v>
@@ -4925,13 +4922,13 @@
         <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E38" t="s">
         <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G38" t="s">
         <v>34</v>
@@ -4967,13 +4964,13 @@
         <v>27</v>
       </c>
       <c r="R38" t="s">
+        <v>340</v>
+      </c>
+      <c r="S38" t="s">
+        <v>32</v>
+      </c>
+      <c r="T38" t="s">
         <v>341</v>
-      </c>
-      <c r="S38" t="s">
-        <v>32</v>
-      </c>
-      <c r="T38" t="s">
-        <v>342</v>
       </c>
       <c r="U38" t="s">
         <v>32</v>
@@ -4990,7 +4987,7 @@
         <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E39" t="s">
         <v>34</v>
@@ -5032,13 +5029,13 @@
         <v>27</v>
       </c>
       <c r="R39" t="s">
+        <v>343</v>
+      </c>
+      <c r="S39" t="s">
+        <v>32</v>
+      </c>
+      <c r="T39" t="s">
         <v>344</v>
-      </c>
-      <c r="S39" t="s">
-        <v>32</v>
-      </c>
-      <c r="T39" t="s">
-        <v>345</v>
       </c>
       <c r="U39" t="s">
         <v>32</v>
@@ -5055,7 +5052,7 @@
         <v>59</v>
       </c>
       <c r="D40" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E40" t="s">
         <v>34</v>
@@ -5097,13 +5094,13 @@
         <v>27</v>
       </c>
       <c r="R40" t="s">
+        <v>346</v>
+      </c>
+      <c r="S40" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" t="s">
         <v>347</v>
-      </c>
-      <c r="S40" t="s">
-        <v>32</v>
-      </c>
-      <c r="T40" t="s">
-        <v>348</v>
       </c>
       <c r="U40" t="s">
         <v>32</v>
@@ -5120,7 +5117,7 @@
         <v>59</v>
       </c>
       <c r="D41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E41" t="s">
         <v>34</v>
@@ -5185,7 +5182,7 @@
         <v>59</v>
       </c>
       <c r="D42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E42" t="s">
         <v>34</v>
@@ -5227,13 +5224,13 @@
         <v>27</v>
       </c>
       <c r="R42" t="s">
+        <v>350</v>
+      </c>
+      <c r="S42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" t="s">
         <v>351</v>
-      </c>
-      <c r="S42" t="s">
-        <v>32</v>
-      </c>
-      <c r="T42" t="s">
-        <v>352</v>
       </c>
       <c r="U42" t="s">
         <v>32</v>
@@ -5250,7 +5247,7 @@
         <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E43" t="s">
         <v>34</v>
@@ -5292,13 +5289,13 @@
         <v>27</v>
       </c>
       <c r="R43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S43" t="s">
         <v>32</v>
       </c>
       <c r="T43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U43" t="s">
         <v>32</v>
@@ -5315,7 +5312,7 @@
         <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E44" t="s">
         <v>34</v>
@@ -5357,13 +5354,13 @@
         <v>27</v>
       </c>
       <c r="R44" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S44" t="s">
         <v>32</v>
       </c>
       <c r="T44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U44" t="s">
         <v>32</v>
@@ -5380,7 +5377,7 @@
         <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E45" t="s">
         <v>34</v>
@@ -5422,13 +5419,13 @@
         <v>27</v>
       </c>
       <c r="R45" t="s">
+        <v>357</v>
+      </c>
+      <c r="S45" t="s">
+        <v>32</v>
+      </c>
+      <c r="T45" t="s">
         <v>358</v>
-      </c>
-      <c r="S45" t="s">
-        <v>32</v>
-      </c>
-      <c r="T45" t="s">
-        <v>359</v>
       </c>
       <c r="U45" t="s">
         <v>32</v>
@@ -5445,7 +5442,7 @@
         <v>160</v>
       </c>
       <c r="D46" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E46" t="s">
         <v>34</v>
@@ -5487,13 +5484,13 @@
         <v>27</v>
       </c>
       <c r="R46" t="s">
+        <v>360</v>
+      </c>
+      <c r="S46" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" t="s">
         <v>361</v>
-      </c>
-      <c r="S46" t="s">
-        <v>32</v>
-      </c>
-      <c r="T46" t="s">
-        <v>362</v>
       </c>
       <c r="U46" t="s">
         <v>32</v>
@@ -5510,7 +5507,7 @@
         <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E47" t="s">
         <v>34</v>
@@ -5552,13 +5549,13 @@
         <v>27</v>
       </c>
       <c r="R47" t="s">
+        <v>363</v>
+      </c>
+      <c r="S47" t="s">
+        <v>32</v>
+      </c>
+      <c r="T47" t="s">
         <v>364</v>
-      </c>
-      <c r="S47" t="s">
-        <v>32</v>
-      </c>
-      <c r="T47" t="s">
-        <v>365</v>
       </c>
       <c r="U47" t="s">
         <v>32</v>
@@ -5575,7 +5572,7 @@
         <v>160</v>
       </c>
       <c r="D48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E48" t="s">
         <v>34</v>
@@ -5617,13 +5614,13 @@
         <v>27</v>
       </c>
       <c r="R48" t="s">
+        <v>366</v>
+      </c>
+      <c r="S48" t="s">
+        <v>32</v>
+      </c>
+      <c r="T48" t="s">
         <v>367</v>
-      </c>
-      <c r="S48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T48" t="s">
-        <v>368</v>
       </c>
       <c r="U48" t="s">
         <v>32</v>
@@ -5640,7 +5637,7 @@
         <v>160</v>
       </c>
       <c r="D49" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E49" t="s">
         <v>34</v>
@@ -5682,13 +5679,13 @@
         <v>27</v>
       </c>
       <c r="R49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S49" t="s">
         <v>32</v>
       </c>
       <c r="T49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U49" t="s">
         <v>32</v>
@@ -5705,7 +5702,7 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E50" t="s">
         <v>34</v>
@@ -5747,13 +5744,13 @@
         <v>27</v>
       </c>
       <c r="R50" t="s">
+        <v>371</v>
+      </c>
+      <c r="S50" t="s">
+        <v>32</v>
+      </c>
+      <c r="T50" t="s">
         <v>372</v>
-      </c>
-      <c r="S50" t="s">
-        <v>32</v>
-      </c>
-      <c r="T50" t="s">
-        <v>373</v>
       </c>
       <c r="U50" t="s">
         <v>32</v>
@@ -5770,7 +5767,7 @@
         <v>160</v>
       </c>
       <c r="D51" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E51" t="s">
         <v>34</v>
@@ -5812,13 +5809,13 @@
         <v>27</v>
       </c>
       <c r="R51" t="s">
+        <v>374</v>
+      </c>
+      <c r="S51" t="s">
+        <v>32</v>
+      </c>
+      <c r="T51" t="s">
         <v>375</v>
-      </c>
-      <c r="S51" t="s">
-        <v>32</v>
-      </c>
-      <c r="T51" t="s">
-        <v>376</v>
       </c>
       <c r="U51" t="s">
         <v>32</v>
@@ -5835,13 +5832,13 @@
         <v>160</v>
       </c>
       <c r="D52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E52" t="s">
         <v>34</v>
       </c>
       <c r="F52" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G52" t="s">
         <v>34</v>
@@ -5874,16 +5871,16 @@
         <v>29</v>
       </c>
       <c r="Q52" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R52" t="s">
+        <v>377</v>
+      </c>
+      <c r="S52" t="s">
+        <v>32</v>
+      </c>
+      <c r="T52" t="s">
         <v>378</v>
-      </c>
-      <c r="S52" t="s">
-        <v>32</v>
-      </c>
-      <c r="T52" t="s">
-        <v>379</v>
       </c>
       <c r="U52" t="s">
         <v>32</v>
@@ -5900,7 +5897,7 @@
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E53" t="s">
         <v>34</v>
@@ -5942,13 +5939,13 @@
         <v>27</v>
       </c>
       <c r="R53" t="s">
+        <v>380</v>
+      </c>
+      <c r="S53" t="s">
+        <v>32</v>
+      </c>
+      <c r="T53" t="s">
         <v>381</v>
-      </c>
-      <c r="S53" t="s">
-        <v>32</v>
-      </c>
-      <c r="T53" t="s">
-        <v>382</v>
       </c>
       <c r="U53" t="s">
         <v>32</v>
@@ -5965,13 +5962,13 @@
         <v>160</v>
       </c>
       <c r="D54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E54" t="s">
         <v>34</v>
       </c>
       <c r="F54" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G54" t="s">
         <v>34</v>
@@ -6004,16 +6001,16 @@
         <v>29</v>
       </c>
       <c r="Q54" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R54" t="s">
+        <v>383</v>
+      </c>
+      <c r="S54" t="s">
+        <v>32</v>
+      </c>
+      <c r="T54" t="s">
         <v>384</v>
-      </c>
-      <c r="S54" t="s">
-        <v>32</v>
-      </c>
-      <c r="T54" t="s">
-        <v>385</v>
       </c>
       <c r="U54" t="s">
         <v>32</v>
@@ -6030,7 +6027,7 @@
         <v>160</v>
       </c>
       <c r="D55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E55" t="s">
         <v>34</v>
@@ -6072,13 +6069,13 @@
         <v>27</v>
       </c>
       <c r="R55" t="s">
+        <v>386</v>
+      </c>
+      <c r="S55" t="s">
+        <v>32</v>
+      </c>
+      <c r="T55" t="s">
         <v>387</v>
-      </c>
-      <c r="S55" t="s">
-        <v>32</v>
-      </c>
-      <c r="T55" t="s">
-        <v>388</v>
       </c>
       <c r="U55" t="s">
         <v>32</v>
@@ -6095,7 +6092,7 @@
         <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E56" t="s">
         <v>34</v>
@@ -6137,13 +6134,13 @@
         <v>27</v>
       </c>
       <c r="R56" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="S56" t="s">
         <v>32</v>
       </c>
       <c r="T56" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="U56" t="s">
         <v>32</v>
@@ -6160,7 +6157,7 @@
         <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E57" t="s">
         <v>34</v>
@@ -6208,7 +6205,7 @@
         <v>32</v>
       </c>
       <c r="T57" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="U57" t="s">
         <v>32</v>
@@ -6225,13 +6222,13 @@
         <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E58" t="s">
         <v>34</v>
       </c>
       <c r="F58" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G58" t="s">
         <v>34</v>
@@ -6264,16 +6261,16 @@
         <v>29</v>
       </c>
       <c r="Q58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R58" t="s">
+        <v>393</v>
+      </c>
+      <c r="S58" t="s">
+        <v>32</v>
+      </c>
+      <c r="T58" t="s">
         <v>394</v>
-      </c>
-      <c r="S58" t="s">
-        <v>32</v>
-      </c>
-      <c r="T58" t="s">
-        <v>395</v>
       </c>
       <c r="U58" t="s">
         <v>32</v>
@@ -6290,7 +6287,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E59" t="s">
         <v>34</v>
@@ -6332,13 +6329,13 @@
         <v>27</v>
       </c>
       <c r="R59" t="s">
+        <v>396</v>
+      </c>
+      <c r="S59" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" t="s">
         <v>397</v>
-      </c>
-      <c r="S59" t="s">
-        <v>32</v>
-      </c>
-      <c r="T59" t="s">
-        <v>398</v>
       </c>
       <c r="U59" t="s">
         <v>32</v>
@@ -6355,7 +6352,7 @@
         <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E60" t="s">
         <v>34</v>
@@ -6397,13 +6394,13 @@
         <v>27</v>
       </c>
       <c r="R60" t="s">
+        <v>399</v>
+      </c>
+      <c r="S60" t="s">
+        <v>32</v>
+      </c>
+      <c r="T60" t="s">
         <v>400</v>
-      </c>
-      <c r="S60" t="s">
-        <v>32</v>
-      </c>
-      <c r="T60" t="s">
-        <v>401</v>
       </c>
       <c r="U60" t="s">
         <v>32</v>
@@ -6420,7 +6417,7 @@
         <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E61" t="s">
         <v>34</v>
@@ -6462,13 +6459,13 @@
         <v>27</v>
       </c>
       <c r="R61" t="s">
+        <v>402</v>
+      </c>
+      <c r="S61" t="s">
+        <v>32</v>
+      </c>
+      <c r="T61" t="s">
         <v>403</v>
-      </c>
-      <c r="S61" t="s">
-        <v>32</v>
-      </c>
-      <c r="T61" t="s">
-        <v>404</v>
       </c>
       <c r="U61" t="s">
         <v>32</v>
@@ -6485,7 +6482,7 @@
         <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E62" t="s">
         <v>34</v>
@@ -6527,13 +6524,13 @@
         <v>27</v>
       </c>
       <c r="R62" t="s">
+        <v>405</v>
+      </c>
+      <c r="S62" t="s">
+        <v>32</v>
+      </c>
+      <c r="T62" t="s">
         <v>406</v>
-      </c>
-      <c r="S62" t="s">
-        <v>32</v>
-      </c>
-      <c r="T62" t="s">
-        <v>407</v>
       </c>
       <c r="U62" t="s">
         <v>32</v>
@@ -6550,7 +6547,7 @@
         <v>225</v>
       </c>
       <c r="D63" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E63" t="s">
         <v>34</v>
@@ -6592,13 +6589,13 @@
         <v>27</v>
       </c>
       <c r="R63" t="s">
+        <v>408</v>
+      </c>
+      <c r="S63" t="s">
+        <v>32</v>
+      </c>
+      <c r="T63" t="s">
         <v>409</v>
-      </c>
-      <c r="S63" t="s">
-        <v>32</v>
-      </c>
-      <c r="T63" t="s">
-        <v>410</v>
       </c>
       <c r="U63" t="s">
         <v>32</v>
@@ -6615,7 +6612,7 @@
         <v>225</v>
       </c>
       <c r="D64" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E64" t="s">
         <v>34</v>
@@ -6657,13 +6654,13 @@
         <v>27</v>
       </c>
       <c r="R64" t="s">
+        <v>411</v>
+      </c>
+      <c r="S64" t="s">
+        <v>32</v>
+      </c>
+      <c r="T64" t="s">
         <v>412</v>
-      </c>
-      <c r="S64" t="s">
-        <v>32</v>
-      </c>
-      <c r="T64" t="s">
-        <v>413</v>
       </c>
       <c r="U64" t="s">
         <v>32</v>
@@ -6680,7 +6677,7 @@
         <v>225</v>
       </c>
       <c r="D65" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E65" t="s">
         <v>34</v>
@@ -6745,7 +6742,7 @@
         <v>225</v>
       </c>
       <c r="D66" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E66" t="s">
         <v>34</v>
@@ -6787,13 +6784,13 @@
         <v>27</v>
       </c>
       <c r="R66" t="s">
+        <v>415</v>
+      </c>
+      <c r="S66" t="s">
+        <v>32</v>
+      </c>
+      <c r="T66" t="s">
         <v>416</v>
-      </c>
-      <c r="S66" t="s">
-        <v>32</v>
-      </c>
-      <c r="T66" t="s">
-        <v>417</v>
       </c>
       <c r="U66" t="s">
         <v>32</v>
@@ -6810,13 +6807,13 @@
         <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E67" t="s">
         <v>34</v>
       </c>
       <c r="F67" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G67" t="s">
         <v>34</v>
@@ -6849,16 +6846,16 @@
         <v>29</v>
       </c>
       <c r="Q67" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="R67" t="s">
+        <v>418</v>
+      </c>
+      <c r="S67" t="s">
+        <v>32</v>
+      </c>
+      <c r="T67" t="s">
         <v>419</v>
-      </c>
-      <c r="S67" t="s">
-        <v>32</v>
-      </c>
-      <c r="T67" t="s">
-        <v>420</v>
       </c>
       <c r="U67" t="s">
         <v>32</v>
@@ -6875,7 +6872,7 @@
         <v>225</v>
       </c>
       <c r="D68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E68" t="s">
         <v>34</v>
@@ -6917,13 +6914,13 @@
         <v>27</v>
       </c>
       <c r="R68" t="s">
+        <v>421</v>
+      </c>
+      <c r="S68" t="s">
+        <v>32</v>
+      </c>
+      <c r="T68" t="s">
         <v>422</v>
-      </c>
-      <c r="S68" t="s">
-        <v>32</v>
-      </c>
-      <c r="T68" t="s">
-        <v>423</v>
       </c>
       <c r="U68" t="s">
         <v>32</v>
@@ -6940,7 +6937,7 @@
         <v>225</v>
       </c>
       <c r="D69" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E69" t="s">
         <v>34</v>
@@ -6982,13 +6979,13 @@
         <v>27</v>
       </c>
       <c r="R69" t="s">
+        <v>424</v>
+      </c>
+      <c r="S69" t="s">
+        <v>32</v>
+      </c>
+      <c r="T69" t="s">
         <v>425</v>
-      </c>
-      <c r="S69" t="s">
-        <v>32</v>
-      </c>
-      <c r="T69" t="s">
-        <v>426</v>
       </c>
       <c r="U69" t="s">
         <v>32</v>
@@ -7005,7 +7002,7 @@
         <v>225</v>
       </c>
       <c r="D70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E70" t="s">
         <v>34</v>
@@ -7047,13 +7044,13 @@
         <v>27</v>
       </c>
       <c r="R70" t="s">
+        <v>427</v>
+      </c>
+      <c r="S70" t="s">
+        <v>32</v>
+      </c>
+      <c r="T70" t="s">
         <v>428</v>
-      </c>
-      <c r="S70" t="s">
-        <v>32</v>
-      </c>
-      <c r="T70" t="s">
-        <v>429</v>
       </c>
       <c r="U70" t="s">
         <v>32</v>
@@ -7070,7 +7067,7 @@
         <v>225</v>
       </c>
       <c r="D71" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E71" t="s">
         <v>34</v>
@@ -7109,16 +7106,16 @@
         <v>29</v>
       </c>
       <c r="Q71" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R71" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S71" t="s">
         <v>32</v>
       </c>
       <c r="T71" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U71" t="s">
         <v>32</v>
@@ -7135,7 +7132,7 @@
         <v>225</v>
       </c>
       <c r="D72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E72" t="s">
         <v>34</v>
@@ -7177,13 +7174,13 @@
         <v>27</v>
       </c>
       <c r="R72" t="s">
+        <v>432</v>
+      </c>
+      <c r="S72" t="s">
+        <v>32</v>
+      </c>
+      <c r="T72" t="s">
         <v>433</v>
-      </c>
-      <c r="S72" t="s">
-        <v>32</v>
-      </c>
-      <c r="T72" t="s">
-        <v>434</v>
       </c>
       <c r="U72" t="s">
         <v>32</v>
@@ -7200,7 +7197,7 @@
         <v>225</v>
       </c>
       <c r="D73" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E73" t="s">
         <v>34</v>
@@ -7242,13 +7239,13 @@
         <v>27</v>
       </c>
       <c r="R73" t="s">
+        <v>435</v>
+      </c>
+      <c r="S73" t="s">
+        <v>32</v>
+      </c>
+      <c r="T73" t="s">
         <v>436</v>
-      </c>
-      <c r="S73" t="s">
-        <v>32</v>
-      </c>
-      <c r="T73" t="s">
-        <v>437</v>
       </c>
       <c r="U73" t="s">
         <v>32</v>
@@ -7265,13 +7262,13 @@
         <v>225</v>
       </c>
       <c r="D74" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E74" t="s">
         <v>34</v>
       </c>
       <c r="F74" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G74" t="s">
         <v>34</v>
@@ -7307,13 +7304,13 @@
         <v>27</v>
       </c>
       <c r="R74" t="s">
+        <v>438</v>
+      </c>
+      <c r="S74" t="s">
+        <v>32</v>
+      </c>
+      <c r="T74" t="s">
         <v>439</v>
-      </c>
-      <c r="S74" t="s">
-        <v>32</v>
-      </c>
-      <c r="T74" t="s">
-        <v>440</v>
       </c>
       <c r="U74" t="s">
         <v>32</v>
@@ -7330,7 +7327,7 @@
         <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E75" t="s">
         <v>34</v>
@@ -7372,13 +7369,13 @@
         <v>27</v>
       </c>
       <c r="R75" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="S75" t="s">
         <v>32</v>
       </c>
       <c r="T75" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U75" t="s">
         <v>32</v>
@@ -7395,7 +7392,7 @@
         <v>225</v>
       </c>
       <c r="D76" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E76" t="s">
         <v>34</v>
@@ -7437,13 +7434,13 @@
         <v>27</v>
       </c>
       <c r="R76" t="s">
+        <v>443</v>
+      </c>
+      <c r="S76" t="s">
+        <v>32</v>
+      </c>
+      <c r="T76" t="s">
         <v>444</v>
-      </c>
-      <c r="S76" t="s">
-        <v>32</v>
-      </c>
-      <c r="T76" t="s">
-        <v>445</v>
       </c>
       <c r="U76" t="s">
         <v>32</v>
@@ -7460,7 +7457,7 @@
         <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E77" t="s">
         <v>34</v>
@@ -7499,13 +7496,13 @@
         <v>29</v>
       </c>
       <c r="R77" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="S77" t="s">
         <v>32</v>
       </c>
       <c r="T77" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="U77" t="s">
         <v>32</v>
@@ -7519,10 +7516,10 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
+        <v>474</v>
+      </c>
+      <c r="D78" t="s">
         <v>475</v>
-      </c>
-      <c r="D78" t="s">
-        <v>476</v>
       </c>
       <c r="E78" t="s">
         <v>34</v>
@@ -7561,13 +7558,13 @@
         <v>29</v>
       </c>
       <c r="R78" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="S78" t="s">
         <v>32</v>
       </c>
       <c r="T78" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="U78" t="s">
         <v>32</v>
@@ -7584,7 +7581,7 @@
         <v>24</v>
       </c>
       <c r="D79" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E79" t="s">
         <v>34</v>
@@ -7623,13 +7620,13 @@
         <v>29</v>
       </c>
       <c r="R79" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S79" t="s">
         <v>32</v>
       </c>
       <c r="T79" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="U79" t="s">
         <v>32</v>
@@ -7694,7 +7691,7 @@
         <v>32</v>
       </c>
       <c r="T80" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="U80" t="s">
         <v>32</v>
@@ -7759,7 +7756,7 @@
         <v>32</v>
       </c>
       <c r="T81" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="U81" t="s">
         <v>32</v>
@@ -7821,7 +7818,7 @@
         <v>32</v>
       </c>
       <c r="T82" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="U82" t="s">
         <v>32</v>
@@ -7886,7 +7883,7 @@
         <v>32</v>
       </c>
       <c r="T83" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="U83" t="s">
         <v>32</v>
@@ -7948,7 +7945,7 @@
         <v>32</v>
       </c>
       <c r="T84" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="U84" t="s">
         <v>32</v>
@@ -8013,7 +8010,7 @@
         <v>32</v>
       </c>
       <c r="T85" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="U85" t="s">
         <v>32</v>
@@ -8075,7 +8072,7 @@
         <v>32</v>
       </c>
       <c r="T86" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U86" t="s">
         <v>32</v>
@@ -8137,7 +8134,7 @@
         <v>32</v>
       </c>
       <c r="T87" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="U87" t="s">
         <v>32</v>
@@ -8199,7 +8196,7 @@
         <v>32</v>
       </c>
       <c r="T88" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="U88" t="s">
         <v>32</v>
@@ -8261,7 +8258,7 @@
         <v>32</v>
       </c>
       <c r="T89" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="U89" t="s">
         <v>32</v>
@@ -8323,7 +8320,7 @@
         <v>32</v>
       </c>
       <c r="T90" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="U90" t="s">
         <v>32</v>
@@ -8388,7 +8385,7 @@
         <v>32</v>
       </c>
       <c r="T91" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="U91" t="s">
         <v>32</v>
@@ -8453,7 +8450,7 @@
         <v>32</v>
       </c>
       <c r="T92" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="U92" t="s">
         <v>32</v>
@@ -8515,7 +8512,7 @@
         <v>32</v>
       </c>
       <c r="T93" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="U93" t="s">
         <v>32</v>
@@ -8577,7 +8574,7 @@
         <v>32</v>
       </c>
       <c r="T94" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U94" t="s">
         <v>32</v>
@@ -8639,7 +8636,7 @@
         <v>32</v>
       </c>
       <c r="T95" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U95" t="s">
         <v>32</v>
@@ -8701,7 +8698,7 @@
         <v>32</v>
       </c>
       <c r="T96" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="U96" t="s">
         <v>32</v>
@@ -8766,7 +8763,7 @@
         <v>32</v>
       </c>
       <c r="T97" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="U97" t="s">
         <v>32</v>
@@ -8828,7 +8825,7 @@
         <v>32</v>
       </c>
       <c r="T98" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="U98" t="s">
         <v>32</v>
@@ -8890,7 +8887,7 @@
         <v>32</v>
       </c>
       <c r="T99" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U99" t="s">
         <v>32</v>
@@ -8952,7 +8949,7 @@
         <v>32</v>
       </c>
       <c r="T100" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="U100" t="s">
         <v>32</v>
@@ -9014,7 +9011,7 @@
         <v>32</v>
       </c>
       <c r="T101" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="U101" t="s">
         <v>32</v>
@@ -9076,7 +9073,7 @@
         <v>32</v>
       </c>
       <c r="T102" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="U102" t="s">
         <v>32</v>
@@ -9141,7 +9138,7 @@
         <v>32</v>
       </c>
       <c r="T103" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="U103" t="s">
         <v>32</v>
@@ -9203,7 +9200,7 @@
         <v>32</v>
       </c>
       <c r="T104" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U104" t="s">
         <v>32</v>
@@ -9265,7 +9262,7 @@
         <v>32</v>
       </c>
       <c r="T105" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="U105" t="s">
         <v>32</v>
@@ -9327,7 +9324,7 @@
         <v>32</v>
       </c>
       <c r="T106" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U106" t="s">
         <v>32</v>
@@ -9389,7 +9386,7 @@
         <v>32</v>
       </c>
       <c r="T107" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="U107" t="s">
         <v>32</v>
@@ -9448,13 +9445,13 @@
         <v>36</v>
       </c>
       <c r="R108" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="S108" t="s">
         <v>32</v>
       </c>
       <c r="T108" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="U108" t="s">
         <v>32</v>
@@ -9516,7 +9513,7 @@
         <v>32</v>
       </c>
       <c r="T109" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="U109" t="s">
         <v>32</v>
@@ -9578,7 +9575,7 @@
         <v>32</v>
       </c>
       <c r="T110" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="U110" t="s">
         <v>32</v>
@@ -9643,7 +9640,7 @@
         <v>32</v>
       </c>
       <c r="T111" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="U111" t="s">
         <v>32</v>
@@ -9708,7 +9705,7 @@
         <v>32</v>
       </c>
       <c r="T112" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U112" t="s">
         <v>32</v>
@@ -9770,7 +9767,7 @@
         <v>32</v>
       </c>
       <c r="T113" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U113" t="s">
         <v>32</v>
@@ -9832,7 +9829,7 @@
         <v>32</v>
       </c>
       <c r="T114" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="U114" t="s">
         <v>32</v>
@@ -9897,7 +9894,7 @@
         <v>32</v>
       </c>
       <c r="T115" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U115" t="s">
         <v>32</v>
@@ -9959,7 +9956,7 @@
         <v>32</v>
       </c>
       <c r="T116" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="U116" t="s">
         <v>32</v>
@@ -10024,7 +10021,7 @@
         <v>32</v>
       </c>
       <c r="T117" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="U117" t="s">
         <v>32</v>
@@ -10086,7 +10083,7 @@
         <v>32</v>
       </c>
       <c r="T118" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="U118" t="s">
         <v>32</v>
@@ -10151,7 +10148,7 @@
         <v>32</v>
       </c>
       <c r="T119" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="U119" t="s">
         <v>32</v>
@@ -10213,7 +10210,7 @@
         <v>32</v>
       </c>
       <c r="T120" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="U120" t="s">
         <v>32</v>
@@ -10278,7 +10275,7 @@
         <v>32</v>
       </c>
       <c r="T121" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="U121" t="s">
         <v>32</v>
@@ -10340,7 +10337,7 @@
         <v>32</v>
       </c>
       <c r="T122" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U122" t="s">
         <v>32</v>
@@ -10402,7 +10399,7 @@
         <v>32</v>
       </c>
       <c r="T123" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U123" t="s">
         <v>32</v>
@@ -10467,7 +10464,7 @@
         <v>32</v>
       </c>
       <c r="T124" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U124" t="s">
         <v>32</v>
@@ -10532,7 +10529,7 @@
         <v>32</v>
       </c>
       <c r="T125" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="U125" t="s">
         <v>32</v>
@@ -10594,7 +10591,7 @@
         <v>32</v>
       </c>
       <c r="T126" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="U126" t="s">
         <v>32</v>
@@ -10617,7 +10614,7 @@
         <v>34</v>
       </c>
       <c r="F127" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G127" t="s">
         <v>28</v>
@@ -10656,7 +10653,7 @@
         <v>32</v>
       </c>
       <c r="T127" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="U127" t="s">
         <v>32</v>
@@ -10721,7 +10718,7 @@
         <v>32</v>
       </c>
       <c r="T128" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="U128" t="s">
         <v>32</v>
@@ -10783,7 +10780,7 @@
         <v>32</v>
       </c>
       <c r="T129" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="U129" t="s">
         <v>32</v>
@@ -10845,7 +10842,7 @@
         <v>32</v>
       </c>
       <c r="T130" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U130" t="s">
         <v>32</v>
@@ -10907,7 +10904,7 @@
         <v>32</v>
       </c>
       <c r="T131" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="U131" t="s">
         <v>32</v>
@@ -10969,7 +10966,7 @@
         <v>32</v>
       </c>
       <c r="T132" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="U132" t="s">
         <v>32</v>
@@ -11034,7 +11031,7 @@
         <v>32</v>
       </c>
       <c r="T133" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="U133" t="s">
         <v>32</v>
@@ -11099,7 +11096,7 @@
         <v>32</v>
       </c>
       <c r="T134" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="U134" t="s">
         <v>32</v>
@@ -11161,7 +11158,7 @@
         <v>32</v>
       </c>
       <c r="T135" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="U135" t="s">
         <v>32</v>
@@ -11226,7 +11223,7 @@
         <v>32</v>
       </c>
       <c r="T136" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="U136" t="s">
         <v>32</v>
@@ -11291,7 +11288,7 @@
         <v>32</v>
       </c>
       <c r="T137" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="U137" t="s">
         <v>32</v>
@@ -11353,7 +11350,7 @@
         <v>32</v>
       </c>
       <c r="T138" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="U138" t="s">
         <v>32</v>
@@ -11415,7 +11412,7 @@
         <v>32</v>
       </c>
       <c r="T139" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="U139" t="s">
         <v>32</v>
@@ -11480,7 +11477,7 @@
         <v>32</v>
       </c>
       <c r="T140" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="U140" t="s">
         <v>32</v>
@@ -11542,7 +11539,7 @@
         <v>32</v>
       </c>
       <c r="T141" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="U141" t="s">
         <v>32</v>
@@ -11604,7 +11601,7 @@
         <v>32</v>
       </c>
       <c r="T142" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="U142" t="s">
         <v>32</v>
@@ -11666,7 +11663,7 @@
         <v>32</v>
       </c>
       <c r="T143" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U143" t="s">
         <v>32</v>
@@ -11731,7 +11728,7 @@
         <v>32</v>
       </c>
       <c r="T144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U144" t="s">
         <v>32</v>
@@ -11796,7 +11793,7 @@
         <v>32</v>
       </c>
       <c r="T145" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="U145" t="s">
         <v>32</v>
@@ -11858,7 +11855,7 @@
         <v>32</v>
       </c>
       <c r="T146" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="U146" t="s">
         <v>32</v>
@@ -11920,7 +11917,7 @@
         <v>32</v>
       </c>
       <c r="T147" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="U147" t="s">
         <v>32</v>
@@ -11985,7 +11982,7 @@
         <v>32</v>
       </c>
       <c r="T148" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="U148" t="s">
         <v>32</v>
@@ -12047,7 +12044,7 @@
         <v>32</v>
       </c>
       <c r="T149" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="U149" t="s">
         <v>32</v>
@@ -12109,7 +12106,7 @@
         <v>32</v>
       </c>
       <c r="T150" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U150" t="s">
         <v>32</v>
@@ -12171,7 +12168,7 @@
         <v>32</v>
       </c>
       <c r="T151" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="U151" t="s">
         <v>32</v>
@@ -12227,7 +12224,7 @@
         <v>29</v>
       </c>
       <c r="Q152" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="R152" t="s">
         <v>179</v>
@@ -12236,7 +12233,7 @@
         <v>32</v>
       </c>
       <c r="T152" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="U152" t="s">
         <v>32</v>
@@ -12292,7 +12289,7 @@
         <v>29</v>
       </c>
       <c r="Q153" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="R153" t="s">
         <v>181</v>
@@ -12301,7 +12298,7 @@
         <v>32</v>
       </c>
       <c r="T153" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="U153" t="s">
         <v>32</v>
@@ -12357,7 +12354,7 @@
         <v>29</v>
       </c>
       <c r="Q154" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="R154" t="s">
         <v>183</v>
@@ -12366,7 +12363,7 @@
         <v>32</v>
       </c>
       <c r="T154" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="U154" t="s">
         <v>32</v>
@@ -12431,7 +12428,7 @@
         <v>32</v>
       </c>
       <c r="T155" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="U155" t="s">
         <v>32</v>
@@ -12493,7 +12490,7 @@
         <v>32</v>
       </c>
       <c r="T156" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="U156" t="s">
         <v>32</v>
@@ -12558,7 +12555,7 @@
         <v>32</v>
       </c>
       <c r="T157" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="U157" t="s">
         <v>32</v>
@@ -12620,7 +12617,7 @@
         <v>32</v>
       </c>
       <c r="T158" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="U158" t="s">
         <v>32</v>
@@ -12682,7 +12679,7 @@
         <v>32</v>
       </c>
       <c r="T159" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="U159" t="s">
         <v>32</v>
@@ -12744,7 +12741,7 @@
         <v>32</v>
       </c>
       <c r="T160" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="U160" t="s">
         <v>32</v>
@@ -12806,7 +12803,7 @@
         <v>32</v>
       </c>
       <c r="T161" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="U161" t="s">
         <v>32</v>
@@ -12868,7 +12865,7 @@
         <v>32</v>
       </c>
       <c r="T162" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="U162" t="s">
         <v>32</v>
@@ -12930,7 +12927,7 @@
         <v>32</v>
       </c>
       <c r="T163" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="U163" t="s">
         <v>32</v>
@@ -12992,7 +12989,7 @@
         <v>32</v>
       </c>
       <c r="T164" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="U164" t="s">
         <v>32</v>
@@ -13054,7 +13051,7 @@
         <v>32</v>
       </c>
       <c r="T165" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="U165" t="s">
         <v>32</v>
@@ -13116,7 +13113,7 @@
         <v>32</v>
       </c>
       <c r="T166" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="U166" t="s">
         <v>32</v>
@@ -13178,7 +13175,7 @@
         <v>32</v>
       </c>
       <c r="T167" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="U167" t="s">
         <v>32</v>
@@ -13240,7 +13237,7 @@
         <v>32</v>
       </c>
       <c r="T168" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U168" t="s">
         <v>32</v>
@@ -13305,7 +13302,7 @@
         <v>32</v>
       </c>
       <c r="T169" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="U169" t="s">
         <v>32</v>
@@ -13361,13 +13358,13 @@
         <v>29</v>
       </c>
       <c r="R170" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S170" t="s">
         <v>32</v>
       </c>
       <c r="T170" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="U170" t="s">
         <v>32</v>
@@ -13432,7 +13429,7 @@
         <v>32</v>
       </c>
       <c r="T171" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U171" t="s">
         <v>32</v>
@@ -13497,7 +13494,7 @@
         <v>32</v>
       </c>
       <c r="T172" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U172" t="s">
         <v>32</v>
@@ -13562,7 +13559,7 @@
         <v>32</v>
       </c>
       <c r="T173" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="U173" t="s">
         <v>32</v>
@@ -13624,7 +13621,7 @@
         <v>32</v>
       </c>
       <c r="T174" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="U174" t="s">
         <v>32</v>
@@ -13686,7 +13683,7 @@
         <v>32</v>
       </c>
       <c r="T175" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="U175" t="s">
         <v>32</v>
@@ -13748,7 +13745,7 @@
         <v>32</v>
       </c>
       <c r="T176" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="U176" t="s">
         <v>32</v>
@@ -13810,7 +13807,7 @@
         <v>32</v>
       </c>
       <c r="T177" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="U177" t="s">
         <v>32</v>
@@ -13872,7 +13869,7 @@
         <v>32</v>
       </c>
       <c r="T178" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="U178" t="s">
         <v>32</v>
@@ -13934,7 +13931,7 @@
         <v>32</v>
       </c>
       <c r="T179" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="U179" t="s">
         <v>32</v>
@@ -13996,7 +13993,7 @@
         <v>32</v>
       </c>
       <c r="T180" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="U180" t="s">
         <v>32</v>
@@ -14061,7 +14058,7 @@
         <v>32</v>
       </c>
       <c r="T181" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U181" t="s">
         <v>32</v>
@@ -14123,7 +14120,7 @@
         <v>32</v>
       </c>
       <c r="T182" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="U182" t="s">
         <v>32</v>
@@ -14185,7 +14182,7 @@
         <v>32</v>
       </c>
       <c r="T183" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U183" t="s">
         <v>32</v>
@@ -14250,7 +14247,7 @@
         <v>32</v>
       </c>
       <c r="T184" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="U184" t="s">
         <v>32</v>
@@ -14312,7 +14309,7 @@
         <v>32</v>
       </c>
       <c r="T185" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="U185" t="s">
         <v>32</v>
@@ -14371,7 +14368,7 @@
         <v>244</v>
       </c>
       <c r="T186" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.3">
@@ -14427,7 +14424,7 @@
         <v>244</v>
       </c>
       <c r="T187" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.3">
@@ -14447,7 +14444,7 @@
         <v>34</v>
       </c>
       <c r="F188" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G188" t="s">
         <v>28</v>
@@ -14483,14 +14480,14 @@
         <v>247</v>
       </c>
       <c r="T188" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E1:U1 B3:U4 E2:U2 C7:G8 C10:G11 C9:E9 G9 C13:G15 C12:D12 G12 C17:G17 C16:E16 G16 C19:G27 C18:E18 G18 C29:G37 C28:E28 G28 C39:G51 C38:E38 G38 C53:G53 C52:E52 G52 C55:G57 C54:E54 G54 C59:G66 C58:E58 G58 C68:G73 C67:E67 G67 C75:G76 C74:E74 G74 S9:U9 R12:U12 U25 R67:U67 R52:U52 R54:U54 R58:U58 R71:U71 P12 D5:G5 C6:G6 P5:U5 P6:U8 P10:U11 P9 P13:U24 P26:U51 P25:S25 P68:U70 P67 P53:U53 P52 P55:U57 P54 P59:U66 P58 P72:U76 P71" numberStoredAsText="1"/>
+    <ignoredError sqref="E1:U1 B3:U4 E2:U2 C7:G8 C10:G11 C9:E9 G9 C13:G15 C12:D12 G12 C17:G17 C16:E16 G16 C19:G27 C18:E18 G18 C29:G37 C28:E28 G28 C39:G51 C38:E38 G38 C53:G53 C52:E52 G52 C55:G57 C54:E54 G54 C59:G66 C58:E58 G58 C68:G73 C67:E67 G67 C75:G76 C74:E74 G74 S9:U9 R12:U12 U25 R67:U67 R52:U52 R54:U54 R58:U58 R71:U71 D5:G5 C6:G6 P5:U5 P6:U8 P10:U11 P9 P13:U24 P26:U51 P25:S25 P68:U70 P67 P53:U53 P52 P55:U57 P54 P59:U66 P58 P72:U76 P71" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14516,7 +14513,7 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -14553,66 +14550,66 @@
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="15" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15" t="s">
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15" t="str">
+      <c r="B5" s="12"/>
+      <c r="C5" s="10" t="str">
         <f>RawData!C2</f>
         <v>용인시</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15">
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="10">
         <f>[1]RawData!B2</f>
         <v>2026</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="14"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="12"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -14633,43 +14630,43 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="12" t="s">
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
@@ -14683,10 +14680,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>8</v>
@@ -14695,14 +14692,14 @@
         <v>9</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -19461,6 +19458,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="N7:N8"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
@@ -19473,14 +19478,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="N7:N8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
